--- a/2024/Develop Software/new/selected/New_Export.xlsx
+++ b/2024/Develop Software/new/selected/New_Export.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Run 11_ untitled" sheetId="2" r:id="rId3"/>
+    <sheet name="Run 7_ PWR" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>time</t>
   </si>
@@ -77,27 +77,6 @@
   </si>
   <si>
     <t>MinMax:1(20)</t>
-  </si>
-  <si>
-    <t>MinMax:1(21)</t>
-  </si>
-  <si>
-    <t>MinMax:1(22)</t>
-  </si>
-  <si>
-    <t>MinMax:1(23)</t>
-  </si>
-  <si>
-    <t>MinMax:1(24)</t>
-  </si>
-  <si>
-    <t>MinMax:1(25)</t>
-  </si>
-  <si>
-    <t>MinMax:1(26)</t>
-  </si>
-  <si>
-    <t>MinMax:1(27)</t>
   </si>
 </sst>
 </file>
@@ -153,7 +132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="true"/>
@@ -164,7 +143,7 @@
     <col min="6" max="6" width="11.33203125" customWidth="true"/>
     <col min="7" max="7" width="11.33203125" customWidth="true"/>
     <col min="8" max="8" width="11.33203125" customWidth="true"/>
-    <col min="9" max="9" width="11.33203125" customWidth="true"/>
+    <col min="9" max="9" width="11.5546875" customWidth="true"/>
     <col min="10" max="10" width="11.33203125" customWidth="true"/>
     <col min="11" max="11" width="12.33203125" customWidth="true"/>
     <col min="12" max="12" width="12.33203125" customWidth="true"/>
@@ -177,13 +156,6 @@
     <col min="19" max="19" width="12.33203125" customWidth="true"/>
     <col min="20" max="20" width="12.33203125" customWidth="true"/>
     <col min="21" max="21" width="12.33203125" customWidth="true"/>
-    <col min="22" max="22" width="12.33203125" customWidth="true"/>
-    <col min="23" max="23" width="12.33203125" customWidth="true"/>
-    <col min="24" max="24" width="12.33203125" customWidth="true"/>
-    <col min="25" max="25" width="12.33203125" customWidth="true"/>
-    <col min="26" max="26" width="12.33203125" customWidth="true"/>
-    <col min="27" max="27" width="12.33203125" customWidth="true"/>
-    <col min="28" max="28" width="12.33203125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -250,112 +222,70 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>229.84999999999999</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>229.84999999999999</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>229.84999999999999</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>229.84999999999999</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F2">
-        <v>229.84999999999999</v>
+        <v>14.324999999999999</v>
       </c>
       <c r="G2">
-        <v>229.84999999999999</v>
+        <v>11.460000000000001</v>
       </c>
       <c r="H2">
-        <v>229.84999999999999</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="I2">
-        <v>229.84999999999999</v>
+        <v>8.1857142857142851</v>
       </c>
       <c r="J2">
-        <v>229.84999999999999</v>
+        <v>7.1624999999999996</v>
       </c>
       <c r="K2">
-        <v>229.84999999999999</v>
+        <v>6.3666666666666663</v>
       </c>
       <c r="L2">
-        <v>229.84999999999999</v>
+        <v>5.7300000000000004</v>
       </c>
       <c r="M2">
-        <v>229.84999999999999</v>
+        <v>5.209090909090909</v>
       </c>
       <c r="N2">
-        <v>229.46000000000001</v>
+        <v>4.7750000000000004</v>
       </c>
       <c r="O2">
-        <v>229.16</v>
+        <v>4.407692307692308</v>
       </c>
       <c r="P2">
-        <v>228.86000000000001</v>
+        <v>4.0928571428571425</v>
       </c>
       <c r="Q2">
-        <v>228.86000000000001</v>
+        <v>3.8199999999999998</v>
       </c>
       <c r="R2">
-        <v>224.70588235294119</v>
+        <v>3.5812499999999998</v>
       </c>
       <c r="S2">
-        <v>212.22222222222223</v>
+        <v>3.3705882352941177</v>
       </c>
       <c r="T2">
-        <v>201.05263157894737</v>
+        <v>3.1833333333333331</v>
       </c>
       <c r="U2">
-        <v>191</v>
-      </c>
-      <c r="V2">
-        <v>181.9047619047619</v>
-      </c>
-      <c r="W2">
-        <v>173.63636363636363</v>
-      </c>
-      <c r="X2">
-        <v>166.08695652173913</v>
-      </c>
-      <c r="Y2">
-        <v>159.16666666666666</v>
-      </c>
-      <c r="Z2">
-        <v>152.80000000000001</v>
-      </c>
-      <c r="AA2">
-        <v>146.92307692307693</v>
-      </c>
-      <c r="AB2">
-        <v>141.4814814814815</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
